--- a/web/templates/pi/PI-template.xlsx
+++ b/web/templates/pi/PI-template.xlsx
@@ -318,7 +318,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="45">
     <border>
       <left/>
       <right/>
@@ -701,11 +701,104 @@
       </top>
       <bottom/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="217">
+  <cellXfs count="263">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1215,6 +1308,126 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="12" fillId="3" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="23" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="15" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="15" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="27" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="28" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="28" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="28" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="28" fillId="6" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="43" fontId="15" fillId="6" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="15" fillId="6" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="28" fillId="6" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="30" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="7" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="12" fillId="7" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="31" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="31" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="31" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="32" fillId="3" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="12" fillId="3" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="43" fontId="32" fillId="3" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="31" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="31" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="31" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="32" fillId="3" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="12" fillId="3" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1888,39 +2101,39 @@
       </c>
     </row>
     <row r="25" ht="44.25" customHeight="1">
-      <c r="A25" s="47" t="n">
+      <c r="A25" s="217" t="n">
         <v>1</v>
       </c>
-      <c r="B25" s="48" t="inlineStr">
+      <c r="B25" s="218" t="inlineStr">
         <is>
           <t>Service Charge for advertisement of Products - KLJ Noida One</t>
         </is>
       </c>
-      <c r="C25" s="49" t="inlineStr">
+      <c r="C25" s="219" t="inlineStr">
         <is>
           <t>INR 6000 +
 15% commission</t>
         </is>
       </c>
-      <c r="D25" s="50" t="inlineStr">
+      <c r="D25" s="220" t="inlineStr">
         <is>
           <t>NOS</t>
         </is>
       </c>
-      <c r="E25" s="51" t="n">
+      <c r="E25" s="221" t="n">
         <v>2</v>
       </c>
-      <c r="F25" s="52" t="n">
+      <c r="F25" s="222" t="n">
         <v>6000</v>
       </c>
-      <c r="G25" s="53" t="n">
+      <c r="G25" s="223" t="n">
         <v>0.18</v>
       </c>
-      <c r="H25" s="54">
+      <c r="H25" s="224">
         <f>(G25*F25)*E25</f>
         <v/>
       </c>
-      <c r="I25" s="55">
+      <c r="I25" s="225">
         <f>F25*E25+H25</f>
         <v/>
       </c>
@@ -1943,39 +2156,39 @@
       <c r="Z25" s="57" t="n"/>
     </row>
     <row r="26" ht="40.5" customHeight="1">
-      <c r="A26" s="47" t="n">
+      <c r="A26" s="217" t="n">
         <v>2</v>
       </c>
-      <c r="B26" s="48" t="inlineStr">
+      <c r="B26" s="218" t="inlineStr">
         <is>
           <t>Service Charge for advertisement of Products - Smartworks Noida</t>
         </is>
       </c>
-      <c r="C26" s="49" t="inlineStr">
+      <c r="C26" s="219" t="inlineStr">
         <is>
           <t>INR 5000 +
 15% commission</t>
         </is>
       </c>
-      <c r="D26" s="50" t="inlineStr">
+      <c r="D26" s="220" t="inlineStr">
         <is>
           <t>NOS</t>
         </is>
       </c>
-      <c r="E26" s="51" t="n">
+      <c r="E26" s="221" t="n">
         <v>2</v>
       </c>
-      <c r="F26" s="52" t="n">
+      <c r="F26" s="222" t="n">
         <v>5000</v>
       </c>
-      <c r="G26" s="53" t="n">
+      <c r="G26" s="223" t="n">
         <v>0.18</v>
       </c>
-      <c r="H26" s="54">
+      <c r="H26" s="224">
         <f>(G26*F26)*E26</f>
         <v/>
       </c>
-      <c r="I26" s="55">
+      <c r="I26" s="225">
         <f>F26*E26+H26</f>
         <v/>
       </c>
@@ -1998,26 +2211,26 @@
       <c r="Z26" s="57" t="n"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="47" t="n">
+      <c r="A27" s="217" t="n">
         <v>3</v>
       </c>
-      <c r="B27" s="48" t="n"/>
-      <c r="C27" s="49" t="n"/>
-      <c r="D27" s="50" t="inlineStr">
+      <c r="B27" s="218" t="n"/>
+      <c r="C27" s="219" t="n"/>
+      <c r="D27" s="220" t="inlineStr">
         <is>
           <t>NOS</t>
         </is>
       </c>
-      <c r="E27" s="51" t="n"/>
-      <c r="F27" s="52" t="n"/>
-      <c r="G27" s="53" t="n">
+      <c r="E27" s="221" t="n"/>
+      <c r="F27" s="222" t="n"/>
+      <c r="G27" s="223" t="n">
         <v>0.18</v>
       </c>
-      <c r="H27" s="59">
+      <c r="H27" s="226">
         <f>I27*18/100</f>
         <v/>
       </c>
-      <c r="I27" s="55">
+      <c r="I27" s="225">
         <f>F27*E27</f>
         <v/>
       </c>
@@ -2040,27 +2253,27 @@
       <c r="Z27" s="57" t="n"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="47">
+      <c r="A28" s="217">
         <f>A27+1</f>
         <v/>
       </c>
-      <c r="B28" s="48" t="n"/>
-      <c r="C28" s="49" t="n"/>
-      <c r="D28" s="50" t="inlineStr">
+      <c r="B28" s="218" t="n"/>
+      <c r="C28" s="219" t="n"/>
+      <c r="D28" s="220" t="inlineStr">
         <is>
           <t>NOS</t>
         </is>
       </c>
-      <c r="E28" s="51" t="n"/>
-      <c r="F28" s="52" t="n"/>
-      <c r="G28" s="53" t="n">
+      <c r="E28" s="221" t="n"/>
+      <c r="F28" s="222" t="n"/>
+      <c r="G28" s="223" t="n">
         <v>0.18</v>
       </c>
-      <c r="H28" s="59">
+      <c r="H28" s="226">
         <f>I28*18/100</f>
         <v/>
       </c>
-      <c r="I28" s="55">
+      <c r="I28" s="225">
         <f>F28*E28</f>
         <v/>
       </c>
@@ -2083,18 +2296,18 @@
       <c r="Z28" s="57" t="n"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="47" t="n"/>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="60" t="n"/>
-      <c r="D29" s="61" t="n"/>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="62" t="n"/>
-      <c r="G29" s="63" t="n"/>
-      <c r="H29" s="64">
+      <c r="A29" s="217" t="n"/>
+      <c r="B29" s="227" t="n"/>
+      <c r="C29" s="228" t="n"/>
+      <c r="D29" s="229" t="n"/>
+      <c r="E29" s="230" t="n"/>
+      <c r="F29" s="231" t="n"/>
+      <c r="G29" s="232" t="n"/>
+      <c r="H29" s="233">
         <f>I29*18/100</f>
         <v/>
       </c>
-      <c r="I29" s="65">
+      <c r="I29" s="234">
         <f>F29*E29</f>
         <v/>
       </c>
@@ -2117,28 +2330,28 @@
       <c r="Z29" s="57" t="n"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="185" t="n"/>
-      <c r="B30" s="186" t="n"/>
-      <c r="C30" s="187" t="inlineStr">
+      <c r="A30" s="235" t="n"/>
+      <c r="B30" s="236" t="n"/>
+      <c r="C30" s="237" t="inlineStr">
         <is>
           <t>Total Qty.</t>
         </is>
       </c>
-      <c r="D30" s="188">
+      <c r="D30" s="238">
         <f>SUM(D25:D29)</f>
         <v/>
       </c>
-      <c r="E30" s="188">
+      <c r="E30" s="238">
         <f>SUM(E25:E29)</f>
         <v/>
       </c>
-      <c r="F30" s="189" t="n"/>
-      <c r="G30" s="190" t="n"/>
-      <c r="H30" s="188">
+      <c r="F30" s="239" t="n"/>
+      <c r="G30" s="240" t="n"/>
+      <c r="H30" s="238">
         <f>SUM(H25:H29)</f>
         <v/>
       </c>
-      <c r="I30" s="191">
+      <c r="I30" s="241">
         <f>SUM(I25,I26)</f>
         <v/>
       </c>
@@ -2161,114 +2374,114 @@
       <c r="Z30" s="72" t="n"/>
     </row>
     <row r="31" ht="33" customHeight="1">
-      <c r="A31" s="192" t="n"/>
-      <c r="B31" s="193" t="inlineStr">
+      <c r="A31" s="242" t="n"/>
+      <c r="B31" s="243" t="inlineStr">
         <is>
           <t>TAX RATE</t>
         </is>
       </c>
-      <c r="C31" s="194" t="inlineStr">
+      <c r="C31" s="244" t="inlineStr">
         <is>
           <t>Taxable Amount</t>
         </is>
       </c>
-      <c r="D31" s="195" t="inlineStr">
+      <c r="D31" s="245" t="inlineStr">
         <is>
           <t>CGST Amt.</t>
         </is>
       </c>
-      <c r="E31" s="195" t="inlineStr">
+      <c r="E31" s="245" t="inlineStr">
         <is>
           <t>SGST Amt.</t>
         </is>
       </c>
-      <c r="F31" s="196" t="inlineStr">
+      <c r="F31" s="246" t="inlineStr">
         <is>
           <t>IGST Amt.</t>
         </is>
       </c>
-      <c r="G31" s="195" t="inlineStr">
+      <c r="G31" s="245" t="inlineStr">
         <is>
           <t>Total Tax</t>
         </is>
       </c>
-      <c r="H31" s="197" t="inlineStr">
+      <c r="H31" s="247" t="inlineStr">
         <is>
           <t>Grand Total (Rs.)</t>
         </is>
       </c>
-      <c r="I31" s="198" t="n">
+      <c r="I31" s="248" t="n">
         <v>25960</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="192" t="n"/>
-      <c r="B32" s="199" t="n">
+      <c r="A32" s="242" t="n"/>
+      <c r="B32" s="249" t="n">
         <v>0.18</v>
       </c>
-      <c r="C32" s="200" t="n">
+      <c r="C32" s="250" t="n">
         <v>22000</v>
       </c>
-      <c r="D32" s="201" t="n"/>
-      <c r="E32" s="201" t="n"/>
-      <c r="F32" s="202">
+      <c r="D32" s="251" t="n"/>
+      <c r="E32" s="251" t="n"/>
+      <c r="F32" s="224">
         <f>C32*18/100</f>
         <v/>
       </c>
-      <c r="G32" s="202">
+      <c r="G32" s="224">
         <f>SUM(D32:F32)</f>
         <v/>
       </c>
-      <c r="H32" s="203" t="n"/>
-      <c r="I32" s="204" t="n"/>
+      <c r="H32" s="252" t="n"/>
+      <c r="I32" s="253" t="n"/>
     </row>
     <row r="33" ht="33" customHeight="1">
-      <c r="A33" s="192" t="n"/>
-      <c r="B33" s="205" t="n"/>
-      <c r="C33" s="206" t="n"/>
-      <c r="D33" s="207" t="n"/>
-      <c r="E33" s="207" t="n"/>
-      <c r="F33" s="208" t="n"/>
-      <c r="G33" s="208" t="n"/>
-      <c r="H33" s="209" t="inlineStr">
+      <c r="A33" s="242" t="n"/>
+      <c r="B33" s="249" t="n"/>
+      <c r="C33" s="250" t="n"/>
+      <c r="D33" s="251" t="n"/>
+      <c r="E33" s="251" t="n"/>
+      <c r="F33" s="224" t="n"/>
+      <c r="G33" s="224" t="n"/>
+      <c r="H33" s="254" t="inlineStr">
         <is>
           <t>For BOHEMIAN CURATIONS PVT. LTD.</t>
         </is>
       </c>
-      <c r="I33" s="210" t="n"/>
+      <c r="I33" s="255" t="n"/>
       <c r="K33" s="180" t="n"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="192" t="n"/>
-      <c r="B34" s="211" t="inlineStr">
+      <c r="A34" s="256" t="n"/>
+      <c r="B34" s="257" t="inlineStr">
         <is>
           <t>Total (Rs.)</t>
         </is>
       </c>
-      <c r="C34" s="212">
+      <c r="C34" s="258">
         <f>(C32+G32)</f>
         <v/>
       </c>
-      <c r="D34" s="213">
+      <c r="D34" s="259">
         <f>SUM(D32:D33)</f>
         <v/>
       </c>
-      <c r="E34" s="212">
+      <c r="E34" s="258">
         <f>SUM(E32:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="214" t="inlineStr">
+      <c r="F34" s="260" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G34" s="214" t="inlineStr">
+      <c r="G34" s="260" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H34" s="215" t="n"/>
-      <c r="I34" s="216" t="n"/>
+      <c r="H34" s="261" t="n"/>
+      <c r="I34" s="262" t="n"/>
     </row>
     <row r="35" ht="16.5" customHeight="1">
       <c r="A35" s="181" t="inlineStr">
